--- a/participants.xlsx
+++ b/participants.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tombola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A680F31C-AF10-4756-8905-19BDD0F971A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84A932F-4DDB-4A17-9A0A-7BBB6EA11A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="413" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>noms</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Edgar</t>
   </si>
   <si>
-    <t>Sofia</t>
-  </si>
-  <si>
     <t>Gazo</t>
   </si>
   <si>
@@ -88,34 +85,55 @@
     <t>Aurelien</t>
   </si>
   <si>
-    <t>Christine</t>
-  </si>
-  <si>
     <t>Christophe</t>
   </si>
   <si>
-    <t>Julie</t>
-  </si>
-  <si>
-    <t>Denis</t>
-  </si>
-  <si>
-    <t>Thibault</t>
-  </si>
-  <si>
-    <t>Coline</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Corentin</t>
-  </si>
-  <si>
-    <t>Auxanne</t>
-  </si>
-  <si>
-    <t>Elisabeth</t>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Benzema</t>
+  </si>
+  <si>
+    <t>Giroud</t>
+  </si>
+  <si>
+    <t>Zidane</t>
+  </si>
+  <si>
+    <t>Euler</t>
+  </si>
+  <si>
+    <t>DPIET</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>Harry</t>
+  </si>
+  <si>
+    <t>Frodon</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Ron</t>
+  </si>
+  <si>
+    <t>Hermione</t>
+  </si>
+  <si>
+    <t>Luck</t>
+  </si>
+  <si>
+    <t>Snow</t>
+  </si>
+  <si>
+    <t>Tyrion</t>
   </si>
 </sst>
 </file>
@@ -486,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
@@ -532,127 +550,152 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/participants.xlsx
+++ b/participants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B8AC6A-5B6C-4819-982E-FD38D5E6B747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C58D174-8DC2-45C9-9444-EC25A84A1AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="collecte (15).csv" sheetId="1" r:id="rId1"/>

--- a/participants.xlsx
+++ b/participants.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C58D174-8DC2-45C9-9444-EC25A84A1AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="2460" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="collecte (15).csv" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="participants_1.csv" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="618">
   <si>
     <t>Nom</t>
   </si>
@@ -734,24 +725,1163 @@
   </si>
   <si>
     <t>hugo.fillet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Brochet</t>
+  </si>
+  <si>
+    <t>Laure</t>
+  </si>
+  <si>
+    <t>+33609644616</t>
+  </si>
+  <si>
+    <t>laure.brochet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>En césure / 3A / autre (étudiant-e)</t>
+  </si>
+  <si>
+    <t>Charley</t>
+  </si>
+  <si>
+    <t>Aubin</t>
+  </si>
+  <si>
+    <t>+33619660034</t>
+  </si>
+  <si>
+    <t>aubin.charley@gmail.com</t>
+  </si>
+  <si>
+    <t>lethuillier</t>
+  </si>
+  <si>
+    <t>justine</t>
+  </si>
+  <si>
+    <t>+33784318416</t>
+  </si>
+  <si>
+    <t>justine.lethuillier@student-cs.fr</t>
+  </si>
+  <si>
+    <t>banzet</t>
+  </si>
+  <si>
+    <t>aude</t>
+  </si>
+  <si>
+    <t>+33618672034</t>
+  </si>
+  <si>
+    <t>aude.banzet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Le Meur</t>
+  </si>
+  <si>
+    <t>+33768553797</t>
+  </si>
+  <si>
+    <t>robin.lemeur@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Najsztat </t>
+  </si>
+  <si>
+    <t>Casimir</t>
+  </si>
+  <si>
+    <t>+33677078501</t>
+  </si>
+  <si>
+    <t>casimir.najsztat@student-cs.fr</t>
+  </si>
+  <si>
+    <t>PALMIER</t>
+  </si>
+  <si>
+    <t>Maeva</t>
+  </si>
+  <si>
+    <t>+33664540365</t>
+  </si>
+  <si>
+    <t>maeva.chansavang@gmail.com</t>
+  </si>
+  <si>
+    <t>Coquet</t>
+  </si>
+  <si>
+    <t>Léa</t>
+  </si>
+  <si>
+    <t>+33782079046</t>
+  </si>
+  <si>
+    <t>lcoquet83@gmail.com</t>
+  </si>
+  <si>
+    <t>Boucher</t>
+  </si>
+  <si>
+    <t>Ian</t>
+  </si>
+  <si>
+    <t>+33644351880</t>
+  </si>
+  <si>
+    <t>ianboucher2207@gmail.com</t>
+  </si>
+  <si>
+    <t>Moriceau</t>
+  </si>
+  <si>
+    <t>Louis</t>
+  </si>
+  <si>
+    <t>+33781689965</t>
+  </si>
+  <si>
+    <t>louis.moriceau@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Buron</t>
+  </si>
+  <si>
+    <t>Mike</t>
+  </si>
+  <si>
+    <t>+33782420857</t>
+  </si>
+  <si>
+    <t>mike.buron@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Jaubert</t>
+  </si>
+  <si>
+    <t>Marion</t>
+  </si>
+  <si>
+    <t>+33695835968</t>
+  </si>
+  <si>
+    <t>marion.jaubert@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Moutet</t>
+  </si>
+  <si>
+    <t>Thibault</t>
+  </si>
+  <si>
+    <t>+33782610302</t>
+  </si>
+  <si>
+    <t>thibault.moutet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>Changhao</t>
+  </si>
+  <si>
+    <t>+33757653900</t>
+  </si>
+  <si>
+    <t>chisaac.cai@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrasson </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur </t>
+  </si>
+  <si>
+    <t>+33766107291</t>
+  </si>
+  <si>
+    <t>arthur.terrasson@free.fr</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>Yiwen</t>
+  </si>
+  <si>
+    <t>+33744715747</t>
+  </si>
+  <si>
+    <t>yiwen.wang.1214@gmail.com</t>
+  </si>
+  <si>
+    <t>Herlent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan </t>
+  </si>
+  <si>
+    <t>+33783303373</t>
+  </si>
+  <si>
+    <t>johan.herlent@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Malfait</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>+33698514062</t>
+  </si>
+  <si>
+    <t>benjamin.malfait27@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trouche </t>
+  </si>
+  <si>
+    <t>+33652157782</t>
+  </si>
+  <si>
+    <t>antoine.trouche@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Dodin</t>
+  </si>
+  <si>
+    <t>Vivien</t>
+  </si>
+  <si>
+    <t>+33679203778</t>
+  </si>
+  <si>
+    <t>vivien.dodin@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Dumortier</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>+33782026818</t>
+  </si>
+  <si>
+    <t>julien.dumortier@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denis </t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>+33651757880</t>
+  </si>
+  <si>
+    <t>edgar.denis@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Toublanc</t>
+  </si>
+  <si>
+    <t>Pauline</t>
+  </si>
+  <si>
+    <t>+33769252821</t>
+  </si>
+  <si>
+    <t>pauline.toublanc@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Musina</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>+33671364728</t>
+  </si>
+  <si>
+    <t>karina.musina@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Nay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alix </t>
+  </si>
+  <si>
+    <t>+33652712736</t>
+  </si>
+  <si>
+    <t>alixasnay@gmail.com</t>
+  </si>
+  <si>
+    <t>Bisch Peuchet</t>
+  </si>
+  <si>
+    <t>Joachim</t>
+  </si>
+  <si>
+    <t>+33782481828</t>
+  </si>
+  <si>
+    <t>bischjoachim@gmail.com</t>
+  </si>
+  <si>
+    <t>Yameogo</t>
+  </si>
+  <si>
+    <t>Olivier</t>
+  </si>
+  <si>
+    <t>+33749799858</t>
+  </si>
+  <si>
+    <t>wendpegbnoma.yameogo@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Ruel</t>
+  </si>
+  <si>
+    <t>Maxime</t>
+  </si>
+  <si>
+    <t>+33652094924</t>
+  </si>
+  <si>
+    <t>maxime.ruel@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Faure</t>
+  </si>
+  <si>
+    <t>+33656679016</t>
+  </si>
+  <si>
+    <t>r.faure75@gmail.com</t>
+  </si>
+  <si>
+    <t>Vienne</t>
+  </si>
+  <si>
+    <t>Colin</t>
+  </si>
+  <si>
+    <t>+33769897987</t>
+  </si>
+  <si>
+    <t>colin.vienne@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Burtin</t>
+  </si>
+  <si>
+    <t>+33651600744</t>
+  </si>
+  <si>
+    <t>benjamin.burtin@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Bechtoldt</t>
+  </si>
+  <si>
+    <t>+33642089938</t>
+  </si>
+  <si>
+    <t>mathieu.bechtoldt@gmail.com</t>
+  </si>
+  <si>
+    <t>de Malherbe</t>
+  </si>
+  <si>
+    <t>+33699193332</t>
+  </si>
+  <si>
+    <t>gauthierdemalherbe@gmail.com</t>
+  </si>
+  <si>
+    <t>Guigui</t>
+  </si>
+  <si>
+    <t>+33643163050</t>
+  </si>
+  <si>
+    <t>antoine.guigui@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Rigaudière</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>+33767016375</t>
+  </si>
+  <si>
+    <t>abel.rigaudiere@gmail.com</t>
+  </si>
+  <si>
+    <t>Letournel</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>+33780045240</t>
+  </si>
+  <si>
+    <t>victor.letournel@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Pigasse</t>
+  </si>
+  <si>
+    <t>+33617567551</t>
+  </si>
+  <si>
+    <t>jules.pigasse@student-cs.fr</t>
+  </si>
+  <si>
+    <t>d'Hébrail</t>
+  </si>
+  <si>
+    <t>Marin</t>
+  </si>
+  <si>
+    <t>+33783709582</t>
+  </si>
+  <si>
+    <t>marindheb@gmail.com</t>
+  </si>
+  <si>
+    <t>Malgrain</t>
+  </si>
+  <si>
+    <t>Auguste</t>
+  </si>
+  <si>
+    <t>+33620353286</t>
+  </si>
+  <si>
+    <t>augustemalgrain@gmail.com</t>
+  </si>
+  <si>
+    <t>Reymondie</t>
+  </si>
+  <si>
+    <t>+33659565510</t>
+  </si>
+  <si>
+    <t>thomas.reymondie@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Benoit</t>
+  </si>
+  <si>
+    <t>+33679498204</t>
+  </si>
+  <si>
+    <t>baptiste.benoit@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>+33624175857</t>
+  </si>
+  <si>
+    <t>thomas.albert@student-cs.fr</t>
+  </si>
+  <si>
+    <t>hosxe</t>
+  </si>
+  <si>
+    <t>come</t>
+  </si>
+  <si>
+    <t>+33651483017</t>
+  </si>
+  <si>
+    <t>come.hosxe@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perret </t>
+  </si>
+  <si>
+    <t>+33782014294</t>
+  </si>
+  <si>
+    <t>antoine.perret@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Perdreau</t>
+  </si>
+  <si>
+    <t>+33651313404</t>
+  </si>
+  <si>
+    <t>thomas.perdreau@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Guillec</t>
+  </si>
+  <si>
+    <t>+33613484366</t>
+  </si>
+  <si>
+    <t>matteo.guillec@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Riclet</t>
+  </si>
+  <si>
+    <t>Titouan</t>
+  </si>
+  <si>
+    <t>+33640913307</t>
+  </si>
+  <si>
+    <t>titouan.riclet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Segaud</t>
+  </si>
+  <si>
+    <t>+33695394455</t>
+  </si>
+  <si>
+    <t>thomas.segaud@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaudichau </t>
+  </si>
+  <si>
+    <t>Alix</t>
+  </si>
+  <si>
+    <t>+33698888321</t>
+  </si>
+  <si>
+    <t>alix.gaudichau@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koetzel </t>
+  </si>
+  <si>
+    <t>Guilhem</t>
+  </si>
+  <si>
+    <t>+33679542165</t>
+  </si>
+  <si>
+    <t>guilhem.koetzel@gmail.com</t>
+  </si>
+  <si>
+    <t>Perez-Duarte</t>
+  </si>
+  <si>
+    <t>Clément</t>
+  </si>
+  <si>
+    <t>+33603674868</t>
+  </si>
+  <si>
+    <t>clement.perezduarte@gmail.com</t>
+  </si>
+  <si>
+    <t>Brandel</t>
+  </si>
+  <si>
+    <t>+33766517724</t>
+  </si>
+  <si>
+    <t>nicolas.brandel@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Villemur</t>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>+33659014716</t>
+  </si>
+  <si>
+    <t>sophie.villemur@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Rivière</t>
+  </si>
+  <si>
+    <t>Aymeric</t>
+  </si>
+  <si>
+    <t>+33631733597</t>
+  </si>
+  <si>
+    <t>aymeric.riviere@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghanassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yacine </t>
+  </si>
+  <si>
+    <t>+33699796558</t>
+  </si>
+  <si>
+    <t>yacine.ghanassi@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Houri</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>+33781803803</t>
+  </si>
+  <si>
+    <t>dadahouri@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebongueng </t>
+  </si>
+  <si>
+    <t>Eloge</t>
+  </si>
+  <si>
+    <t>+33621229685</t>
+  </si>
+  <si>
+    <t>eloge.ebongueng@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Barsalou</t>
+  </si>
+  <si>
+    <t>Quentin</t>
+  </si>
+  <si>
+    <t>+33637762753</t>
+  </si>
+  <si>
+    <t>quentbarsa@gmail.com</t>
+  </si>
+  <si>
+    <t>Ros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raphaël </t>
+  </si>
+  <si>
+    <t>+33762321713</t>
+  </si>
+  <si>
+    <t>raphael.ros@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA MARCANDELLI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan </t>
+  </si>
+  <si>
+    <t>+33660865707</t>
+  </si>
+  <si>
+    <t>tristan.garcia-marcandelli@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Tissot</t>
+  </si>
+  <si>
+    <t>Erwan</t>
+  </si>
+  <si>
+    <t>+33626624971</t>
+  </si>
+  <si>
+    <t>erwan.tissot94@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dzouossia Mozie </t>
+  </si>
+  <si>
+    <t>Keli Xaviera</t>
+  </si>
+  <si>
+    <t>+33753348558</t>
+  </si>
+  <si>
+    <t>keli-xaviera.dzouossia-mozie@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Bureau</t>
+  </si>
+  <si>
+    <t>Mathys</t>
+  </si>
+  <si>
+    <t>+33777972495</t>
+  </si>
+  <si>
+    <t>Mathys.bureau@student-cs.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bretaudeau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorian </t>
+  </si>
+  <si>
+    <t>+33768754712</t>
+  </si>
+  <si>
+    <t>dorian.bretaudeau@student-cs.fr</t>
+  </si>
+  <si>
+    <t>o.lavalsebire@gmail.com</t>
+  </si>
+  <si>
+    <t>MASTERNAK</t>
+  </si>
+  <si>
+    <t>Célia</t>
+  </si>
+  <si>
+    <t>+33601862716</t>
+  </si>
+  <si>
+    <t>celia.masternak@hotmail.fr</t>
+  </si>
+  <si>
+    <t>Clement</t>
+  </si>
+  <si>
+    <t>Alexis</t>
+  </si>
+  <si>
+    <t>+33767769375</t>
+  </si>
+  <si>
+    <t>alexisclement6@gmail.com</t>
+  </si>
+  <si>
+    <t>Bichet</t>
+  </si>
+  <si>
+    <t>+33788782707</t>
+  </si>
+  <si>
+    <t>bichethugo1211@gmail.com</t>
+  </si>
+  <si>
+    <t>Bringer</t>
+  </si>
+  <si>
+    <t>Emilie</t>
+  </si>
+  <si>
+    <t>+33670350524</t>
+  </si>
+  <si>
+    <t>emilie.bringer@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Pradeau</t>
+  </si>
+  <si>
+    <t>Domitille</t>
+  </si>
+  <si>
+    <t>+33620055631</t>
+  </si>
+  <si>
+    <t>domitille.pradeau@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Delest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aurélien </t>
+  </si>
+  <si>
+    <t>+33761817869</t>
+  </si>
+  <si>
+    <t>aurelien.delest@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Lott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théophile </t>
+  </si>
+  <si>
+    <t>+33618613734</t>
+  </si>
+  <si>
+    <t>theophile.lott@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Goudon</t>
+  </si>
+  <si>
+    <t>+33767212208</t>
+  </si>
+  <si>
+    <t>oscar.goudon-de-lalande@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Joudinaud</t>
+  </si>
+  <si>
+    <t>Wandrille</t>
+  </si>
+  <si>
+    <t>+33769203128</t>
+  </si>
+  <si>
+    <t>wandrille.joudinaud@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Delavanne</t>
+  </si>
+  <si>
+    <t>Marthe</t>
+  </si>
+  <si>
+    <t>+33760490002</t>
+  </si>
+  <si>
+    <t>marthe.delavanne@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Gallone</t>
+  </si>
+  <si>
+    <t>Priska</t>
+  </si>
+  <si>
+    <t>+33652811004</t>
+  </si>
+  <si>
+    <t>priska.gallone@student-cs.fr</t>
+  </si>
+  <si>
+    <t>SANDRARD</t>
+  </si>
+  <si>
+    <t>ETIENNE</t>
+  </si>
+  <si>
+    <t>+33610360880</t>
+  </si>
+  <si>
+    <t>etienne.sandrard@gmail.com</t>
+  </si>
+  <si>
+    <t>Vasseur Wietzke</t>
+  </si>
+  <si>
+    <t>Lena</t>
+  </si>
+  <si>
+    <t>+33782096213</t>
+  </si>
+  <si>
+    <t>lena.vasseur-wietzke@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Abou Chebel</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>+33604755794</t>
+  </si>
+  <si>
+    <t>georgia.achebel@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Binard</t>
+  </si>
+  <si>
+    <t>Eliott</t>
+  </si>
+  <si>
+    <t>+33781968985</t>
+  </si>
+  <si>
+    <t>eliott.binard@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Govaere</t>
+  </si>
+  <si>
+    <t>+33767268082</t>
+  </si>
+  <si>
+    <t>govaerecamille@gmail.com</t>
+  </si>
+  <si>
+    <t>Aurèle</t>
+  </si>
+  <si>
+    <t>Gallard</t>
+  </si>
+  <si>
+    <t>+33618354910</t>
+  </si>
+  <si>
+    <t>aurele.gallard@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Gourdoux</t>
+  </si>
+  <si>
+    <t>Matis</t>
+  </si>
+  <si>
+    <t>+33695780781</t>
+  </si>
+  <si>
+    <t>matis.gourdoux@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>+33761369562</t>
+  </si>
+  <si>
+    <t>louis.page@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Corrard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre </t>
+  </si>
+  <si>
+    <t>+33663462732</t>
+  </si>
+  <si>
+    <t>alexandre.corrard@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Demarcy</t>
+  </si>
+  <si>
+    <t>Adrian</t>
+  </si>
+  <si>
+    <t>+33634622089</t>
+  </si>
+  <si>
+    <t>ademarcy34@gmail.com</t>
+  </si>
+  <si>
+    <t>Huber</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>+33767280074</t>
+  </si>
+  <si>
+    <t>gaston.huber@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Madhavan</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>+33667689971</t>
+  </si>
+  <si>
+    <t>divya.madhavan@centralesupelec.fr</t>
+  </si>
+  <si>
+    <t>Membre de l'administration / autre</t>
+  </si>
+  <si>
+    <t>Knecht</t>
+  </si>
+  <si>
+    <t>Axel</t>
+  </si>
+  <si>
+    <t>+33675105625</t>
+  </si>
+  <si>
+    <t>axel.knecht@outlook.fr</t>
+  </si>
+  <si>
+    <t>Haddad</t>
+  </si>
+  <si>
+    <t>Emett</t>
+  </si>
+  <si>
+    <t>emett.haddad@ens-paris-saclay.fr</t>
+  </si>
+  <si>
+    <t>erwan.tissot@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Bonnet</t>
+  </si>
+  <si>
+    <t>Johan</t>
+  </si>
+  <si>
+    <t>+33781985484</t>
+  </si>
+  <si>
+    <t>johan.bonnet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>D’argenlieu</t>
+  </si>
+  <si>
+    <t>Etienne</t>
+  </si>
+  <si>
+    <t>+33619974872</t>
+  </si>
+  <si>
+    <t>edargenlieu@gmail.com</t>
+  </si>
+  <si>
+    <t>Lyonnais</t>
+  </si>
+  <si>
+    <t>Maximilien</t>
+  </si>
+  <si>
+    <t>+33642159186</t>
+  </si>
+  <si>
+    <t>maximilien.lyonnais@hotmail.fr</t>
+  </si>
+  <si>
+    <t>Duret</t>
+  </si>
+  <si>
+    <t>+33665690825</t>
+  </si>
+  <si>
+    <t>martin.duret@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Roth</t>
+  </si>
+  <si>
+    <t>+33768704982</t>
+  </si>
+  <si>
+    <t>martin.roth@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Petit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">François </t>
+  </si>
+  <si>
+    <t>+33769590556</t>
+  </si>
+  <si>
+    <t>francois.petit@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Pisarik</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>+33768643864</t>
+  </si>
+  <si>
+    <t>jan.pisarik23@gmail.com</t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t>+33652195003</t>
+  </si>
+  <si>
+    <t>benoit.massenet@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Glatigny</t>
+  </si>
+  <si>
+    <t>+33648088944</t>
+  </si>
+  <si>
+    <t>romain.glatigny@student-cs.fr</t>
+  </si>
+  <si>
+    <t>Saillard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne-Laure </t>
+  </si>
+  <si>
+    <t>+33760022703</t>
+  </si>
+  <si>
+    <t>al.saillard00@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diaz--furling </t>
+  </si>
+  <si>
+    <t>Romane</t>
+  </si>
+  <si>
+    <t>+33631123747</t>
+  </si>
+  <si>
+    <t>romane.diazfurling@student-cs.fr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d/m/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="d/m/yyyy hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -762,44 +1892,39 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -989,20 +2114,17 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +2156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,7 +2185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1083,13 +2205,13 @@
         <v>14</v>
       </c>
       <c r="I3" s="2">
-        <v>45273.419502314813</v>
+        <v>45273.41950231481</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1109,13 +2231,13 @@
         <v>14</v>
       </c>
       <c r="I4" s="2">
-        <v>45273.497187499997</v>
+        <v>45273.4971875</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -1135,13 +2257,13 @@
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>45273.495763888888</v>
+        <v>45273.49576388889</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -1167,7 +2289,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -1193,7 +2315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -1225,7 +2347,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -1251,13 +2373,13 @@
         <v>15</v>
       </c>
       <c r="I9" s="2">
-        <v>45273.511446759258</v>
+        <v>45273.51144675926</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -1283,7 +2405,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -1309,7 +2431,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -1329,13 +2451,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="2">
-        <v>45273.519131944442</v>
+        <v>45273.51913194444</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1358,13 +2480,13 @@
         <v>15</v>
       </c>
       <c r="I13" s="2">
-        <v>45273.521643518521</v>
+        <v>45273.52164351852</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>67</v>
       </c>
@@ -1387,13 +2509,13 @@
         <v>15</v>
       </c>
       <c r="I14" s="2">
-        <v>45273.521909722222</v>
+        <v>45273.52190972222</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>71</v>
       </c>
@@ -1422,7 +2544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
@@ -1448,7 +2570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>79</v>
       </c>
@@ -1468,13 +2590,13 @@
         <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>45273.533379629633</v>
+        <v>45273.53337962963</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
@@ -1494,13 +2616,13 @@
         <v>30</v>
       </c>
       <c r="I18" s="2">
-        <v>45273.535763888889</v>
+        <v>45273.53576388889</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>87</v>
       </c>
@@ -1520,13 +2642,13 @@
         <v>30</v>
       </c>
       <c r="I19" s="2">
-        <v>45273.535810185182</v>
+        <v>45273.53581018518</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>91</v>
       </c>
@@ -1546,13 +2668,13 @@
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>45273.596539351849</v>
+        <v>45273.59653935185</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>95</v>
       </c>
@@ -1572,13 +2694,13 @@
         <v>30</v>
       </c>
       <c r="I21" s="2">
-        <v>45273.627256944441</v>
+        <v>45273.62725694444</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>99</v>
       </c>
@@ -1598,13 +2720,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="2">
-        <v>45273.627442129633</v>
+        <v>45273.62744212963</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>103</v>
       </c>
@@ -1624,13 +2746,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="2">
-        <v>45273.633449074077</v>
+        <v>45273.63344907408</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>107</v>
       </c>
@@ -1656,7 +2778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
@@ -1676,13 +2798,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="2">
-        <v>45273.713125000002</v>
+        <v>45273.713125</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>115</v>
       </c>
@@ -1708,7 +2830,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>118</v>
       </c>
@@ -1728,13 +2850,13 @@
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>45273.802164351851</v>
+        <v>45273.80216435185</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>122</v>
       </c>
@@ -1754,13 +2876,13 @@
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>45273.889490740738</v>
+        <v>45273.88949074074</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="1" t="s">
         <v>125</v>
       </c>
@@ -1786,7 +2908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>129</v>
       </c>
@@ -1812,7 +2934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="1" t="s">
         <v>133</v>
       </c>
@@ -1832,13 +2954,13 @@
         <v>30</v>
       </c>
       <c r="I31" s="2">
-        <v>45274.484479166669</v>
+        <v>45274.48447916667</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="1" t="s">
         <v>137</v>
       </c>
@@ -1858,13 +2980,13 @@
         <v>40</v>
       </c>
       <c r="I32" s="2">
-        <v>45274.489027777781</v>
+        <v>45274.48902777778</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="1" t="s">
         <v>140</v>
       </c>
@@ -1884,13 +3006,13 @@
         <v>14</v>
       </c>
       <c r="I33" s="2">
-        <v>45274.495428240742</v>
+        <v>45274.49542824074</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="1" t="s">
         <v>144</v>
       </c>
@@ -1919,7 +3041,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="1" t="s">
         <v>150</v>
       </c>
@@ -1939,13 +3061,13 @@
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>45274.500787037039</v>
+        <v>45274.50078703704</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="1" t="s">
         <v>154</v>
       </c>
@@ -1965,13 +3087,13 @@
         <v>14</v>
       </c>
       <c r="I36" s="2">
-        <v>45274.506504629629</v>
+        <v>45274.50650462963</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="1" t="s">
         <v>158</v>
       </c>
@@ -1997,7 +3119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="1" t="s">
         <v>162</v>
       </c>
@@ -2017,13 +3139,13 @@
         <v>14</v>
       </c>
       <c r="I38" s="2">
-        <v>45274.511435185188</v>
+        <v>45274.51143518519</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="1" t="s">
         <v>166</v>
       </c>
@@ -2043,13 +3165,13 @@
         <v>14</v>
       </c>
       <c r="I39" s="2">
-        <v>45274.511006944442</v>
+        <v>45274.51100694444</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="1" t="s">
         <v>170</v>
       </c>
@@ -2075,7 +3197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="1" t="s">
         <v>174</v>
       </c>
@@ -2098,13 +3220,13 @@
         <v>15</v>
       </c>
       <c r="I41" s="2">
-        <v>45274.512592592589</v>
+        <v>45274.51259259259</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="1" t="s">
         <v>178</v>
       </c>
@@ -2124,13 +3246,13 @@
         <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>45274.512731481482</v>
+        <v>45274.51273148148</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="1" t="s">
         <v>182</v>
       </c>
@@ -2150,13 +3272,13 @@
         <v>14</v>
       </c>
       <c r="I43" s="2">
-        <v>45274.513622685183</v>
+        <v>45274.51362268518</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="1" t="s">
         <v>186</v>
       </c>
@@ -2182,7 +3304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="1" t="s">
         <v>189</v>
       </c>
@@ -2202,13 +3324,13 @@
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>45274.517638888887</v>
+        <v>45274.51763888889</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="1" t="s">
         <v>192</v>
       </c>
@@ -2234,7 +3356,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="1" t="s">
         <v>196</v>
       </c>
@@ -2260,7 +3382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="1" t="s">
         <v>200</v>
       </c>
@@ -2286,7 +3408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -2306,13 +3428,13 @@
         <v>14</v>
       </c>
       <c r="I49" s="2">
-        <v>45274.567106481481</v>
+        <v>45274.56710648148</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="1" t="s">
         <v>207</v>
       </c>
@@ -2332,13 +3454,13 @@
         <v>40</v>
       </c>
       <c r="I50" s="2">
-        <v>45274.574247685188</v>
+        <v>45274.57424768519</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51" s="1" t="s">
         <v>211</v>
       </c>
@@ -2364,7 +3486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="1" t="s">
         <v>215</v>
       </c>
@@ -2393,7 +3515,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="1" t="s">
         <v>219</v>
       </c>
@@ -2413,13 +3535,13 @@
         <v>14</v>
       </c>
       <c r="I53" s="2">
-        <v>45274.588935185187</v>
+        <v>45274.58893518519</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="1" t="s">
         <v>223</v>
       </c>
@@ -2439,13 +3561,13 @@
         <v>14</v>
       </c>
       <c r="I54" s="2">
-        <v>45274.590601851851</v>
+        <v>45274.59060185185</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="1" t="s">
         <v>227</v>
       </c>
@@ -2465,13 +3587,13 @@
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>45274.591423611113</v>
+        <v>45274.59142361111</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="1" t="s">
         <v>231</v>
       </c>
@@ -2491,13 +3613,13 @@
         <v>14</v>
       </c>
       <c r="I56" s="2">
-        <v>45274.605243055557</v>
+        <v>45274.60524305556</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="1" t="s">
         <v>235</v>
       </c>
@@ -2517,13 +3639,2776 @@
         <v>40</v>
       </c>
       <c r="I57" s="2">
-        <v>45274.610150462962</v>
+        <v>45274.61015046296</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>41</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2">
+        <v>45274.64501157407</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2">
+        <v>45274.67222222222</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="2">
+        <v>45274.67238425926</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="2">
+        <v>45274.67525462963</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2">
+        <v>45274.67668981481</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2">
+        <v>45274.68349537037</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I64" s="2">
+        <v>45274.68101851852</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="2">
+        <v>45274.68797453704</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2">
+        <v>45274.694085648145</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2">
+        <v>45274.694386574076</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="2">
+        <v>45274.700833333336</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2">
+        <v>45274.72212962963</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="2">
+        <v>45274.74086805555</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="2">
+        <v>45274.74532407407</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="2">
+        <v>45274.773368055554</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I73" s="2">
+        <v>45274.80515046296</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="2">
+        <v>45274.841157407405</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="2">
+        <v>45274.84065972222</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="2">
+        <v>45274.84143518518</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2">
+        <v>45274.859444444446</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="2">
+        <v>45274.959502314814</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="2">
+        <v>45275.25021990741</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45275.37428240741</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2">
+        <v>45275.39885416667</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2">
+        <v>45275.44876157407</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I83" s="2">
+        <v>45275.517696759256</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" s="2">
+        <v>45275.525717592594</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="2">
+        <v>45275.5343287037</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I86" s="2">
+        <v>45275.549837962964</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="2">
+        <v>45275.54997685185</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88" s="2">
+        <v>45275.592453703706</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="2">
+        <v>45275.5959375</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" s="2">
+        <v>45275.65819444445</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2">
+        <v>45275.71328703704</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2">
+        <v>45275.774930555555</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="2">
+        <v>45275.84119212963</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" s="2">
+        <v>45276.50047453704</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2">
+        <v>45276.54201388889</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" s="2">
+        <v>45276.67543981481</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="2">
+        <v>45276.73657407407</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="2">
+        <v>45276.99170138889</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2">
+        <v>45277.59957175926</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="2">
+        <v>45277.60030092593</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="2">
+        <v>45277.690567129626</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" s="2">
+        <v>45277.88527777778</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="2">
+        <v>45277.92655092593</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2">
+        <v>45278.45474537037</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="2">
+        <v>45278.56332175926</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2">
+        <v>45278.57056712963</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2">
+        <v>45278.60089120371</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" s="2">
+        <v>45278.61225694444</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I109" s="2">
+        <v>45278.63395833333</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2">
+        <v>45278.65820601852</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="2">
+        <v>45278.77545138889</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2">
+        <v>45278.808229166665</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I113" s="2">
+        <v>45278.861759259256</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="2">
+        <v>45279.05358796296</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2">
+        <v>45279.36326388889</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" s="2">
+        <v>45279.465949074074</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2">
+        <v>45279.475277777776</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="2">
+        <v>45279.66274305555</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" s="2">
+        <v>45279.70402777778</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="2">
+        <v>45280.493726851855</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="2">
+        <v>45280.50534722222</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2">
+        <v>45280.50659722222</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="2">
+        <v>45280.50711805555</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2">
+        <v>45280.51644675926</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I125" s="2">
+        <v>45280.51746527778</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I126" s="2">
+        <v>45280.51994212963</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I127" s="2">
+        <v>45280.52758101852</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="2">
+        <v>45280.55061342593</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2">
+        <v>45280.65300925926</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="2">
+        <v>45280.732777777775</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" s="2">
+        <v>45281.02804398148</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="2">
+        <v>45281.077511574076</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" s="2">
+        <v>45281.39414351852</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="2">
+        <v>45281.40818287037</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2">
+        <v>45281.451145833336</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2">
+        <v>45281.461168981485</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" s="2">
+        <v>45281.46775462963</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2">
+        <v>45281.4740625</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="2">
+        <v>45281.49532407407</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I140" s="2">
+        <v>45281.52689814815</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2">
+        <v>45281.53328703704</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I142" s="2">
+        <v>45281.552037037036</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2">
+        <v>45281.557650462964</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I144" s="2">
+        <v>45281.55876157407</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I145" s="2">
+        <v>45281.56284722222</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I146" s="2">
+        <v>45281.56576388889</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2">
+        <v>45281.577199074076</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2">
+        <v>45281.598287037035</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2">
+        <v>45281.59773148148</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2">
+        <v>45281.59789351852</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2">
+        <v>45281.60053240741</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2">
+        <v>45281.616261574076</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2">
+        <v>45281.617106481484</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" s="2">
+        <v>45281.62221064815</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2">
+        <v>45281.62527777778</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I156" s="2">
+        <v>45281.703125</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2">
+        <v>45281.713854166665</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="2">
+        <v>45281.7156712963</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I159" s="2">
+        <v>45281.72385416667</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2">
+        <v>45281.72447916667</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I161" s="2">
+        <v>45281.73024305556</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I162" s="2">
+        <v>45281.732719907406</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>